--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487809_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487809_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.3832</v>
+        <v>7.6316</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1927</v>
+        <v>3.7641</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1905</v>
+        <v>3.8675</v>
       </c>
       <c r="G2" t="n">
         <v>3.759</v>
@@ -610,13 +610,13 @@
         <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1673</v>
+        <v>1.4157</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7111</v>
+        <v>0.2824</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4562</v>
+        <v>1.1333</v>
       </c>
       <c r="V2" t="n">
         <v>0.5838</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.9084</v>
+        <v>7.5719</v>
       </c>
       <c r="E3" t="n">
-        <v>7.2022</v>
+        <v>7.6308</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2938</v>
+        <v>-0.0589</v>
       </c>
       <c r="G3" t="n">
         <v>6.677</v>
@@ -688,13 +688,13 @@
         <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4554</v>
+        <v>0.2081</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6524</v>
+        <v>-0.2238</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1971</v>
+        <v>0.4319</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3538</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3163</v>
+        <v>5.5893</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1803</v>
+        <v>3.3947</v>
       </c>
       <c r="F4" t="n">
-        <v>2.136</v>
+        <v>2.1947</v>
       </c>
       <c r="G4" t="n">
         <v>6.563</v>
@@ -766,13 +766,13 @@
         <v>1.4568</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6224</v>
+        <v>-0.3493</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4567</v>
+        <v>-0.2424</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1657</v>
+        <v>-0.107</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9433</v>
+        <v>2.0711</v>
       </c>
       <c r="E5" t="n">
-        <v>1.087</v>
+        <v>0.9798</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8563</v>
+        <v>1.0912</v>
       </c>
       <c r="G5" t="n">
         <v>1.8455</v>
@@ -844,13 +844,13 @@
         <v>1.4568</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0385</v>
+        <v>0.1662</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1272</v>
+        <v>0.02</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0887</v>
+        <v>0.1462</v>
       </c>
       <c r="V5" t="n">
         <v>-1.3975</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. BELLO MOURE</t>
+          <t>S. NDIAYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5543</v>
+        <v>2.0329</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3</v>
+        <v>0.7923</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7457</v>
+        <v>1.2406</v>
       </c>
       <c r="G6" t="n">
-        <v>0.748</v>
+        <v>0.5712</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2386</v>
+        <v>0.7973</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5094</v>
+        <v>-0.2261</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6136</v>
+        <v>2.1267</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9654</v>
+        <v>1.4303</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6482</v>
+        <v>0.6964</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8656</v>
+        <v>-1.5555</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7268</v>
+        <v>-0.6329</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1388</v>
+        <v>-0.9225</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0406</v>
+        <v>0.2081</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0406</v>
+        <v>2.2893</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1008</v>
+        <v>1.1298</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6864</v>
+        <v>0.7468</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4143</v>
+        <v>0.383</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.3351</v>
+        <v>0.1238</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.3351</v>
+        <v>0.1238</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3006</v>
+        <v>1.4768</v>
       </c>
       <c r="E7" t="n">
         <v>0.5434</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7573</v>
+        <v>0.9334</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4624</v>
@@ -1000,13 +1000,13 @@
         <v>1.6649</v>
       </c>
       <c r="S7" t="n">
-        <v>0.428</v>
+        <v>0.6041</v>
       </c>
       <c r="T7" t="n">
         <v>0.1272</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3008</v>
+        <v>0.4769</v>
       </c>
       <c r="V7" t="n">
         <v>1.7513</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. NDIAYE</t>
+          <t>F. BELLO MOURE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0773</v>
+        <v>0.54</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0422</v>
+        <v>2.5499</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0351</v>
+        <v>-2.01</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5712</v>
+        <v>0.748</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7973</v>
+        <v>0.2386</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2261</v>
+        <v>0.5094</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1267</v>
+        <v>1.6136</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4303</v>
+        <v>0.9654</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6964</v>
+        <v>0.6482</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5555</v>
+        <v>-0.8656</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6329</v>
+        <v>-0.7268</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9225</v>
+        <v>-0.1388</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2081</v>
+        <v>1.0406</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2893</v>
+        <v>1.0406</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1742</v>
+        <v>1.0864</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0033</v>
+        <v>0.9363</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1775</v>
+        <v>0.1501</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1238</v>
+        <v>-2.3351</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1238</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6885</v>
+        <v>0.3464</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2406</v>
+        <v>1.1334</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5521</v>
+        <v>-0.787</v>
       </c>
       <c r="G9" t="n">
         <v>2.516</v>
@@ -1156,13 +1156,13 @@
         <v>1.8731</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2755</v>
+        <v>0.9334</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1272</v>
+        <v>0.02</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1483</v>
+        <v>0.9134</v>
       </c>
       <c r="V9" t="n">
         <v>-0.8137</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1612</v>
+        <v>-0.5271</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0199</v>
+        <v>-1.5912</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8586</v>
+        <v>1.0641</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2701</v>
@@ -1312,13 +1312,13 @@
         <v>1.2487</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2668</v>
+        <v>0.3673</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1272</v>
+        <v>0.5558</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.394</v>
+        <v>-0.1885</v>
       </c>
       <c r="V11" t="n">
         <v>1.1675</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4026</v>
+        <v>-2.1248</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4492</v>
+        <v>0.0206</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8518</v>
+        <v>-2.1454</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5149</v>
@@ -1390,13 +1390,13 @@
         <v>0.6244</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4692</v>
+        <v>0.747</v>
       </c>
       <c r="T12" t="n">
-        <v>0.972</v>
+        <v>0.5434</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4972</v>
+        <v>0.2036</v>
       </c>
       <c r="V12" t="n">
         <v>-1.9813</v>
@@ -1426,10 +1426,10 @@
         <v>24.562</v>
       </c>
       <c r="E13" t="n">
-        <v>19.1716</v>
+        <v>19.1717</v>
       </c>
       <c r="F13" t="n">
-        <v>5.390400000000001</v>
+        <v>5.3902</v>
       </c>
       <c r="G13" t="n">
         <v>17.7371</v>
@@ -1453,10 +1453,10 @@
         <v>-2.104000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.349300000000001</v>
+        <v>-5.349299999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>3.245399999999999</v>
+        <v>3.2454</v>
       </c>
       <c r="P13" t="n">
         <v>3.1218</v>
@@ -1468,13 +1468,13 @@
         <v>15.6089</v>
       </c>
       <c r="S13" t="n">
-        <v>6.958</v>
+        <v>6.9578</v>
       </c>
       <c r="T13" t="n">
-        <v>3.415</v>
+        <v>3.4148</v>
       </c>
       <c r="U13" t="n">
-        <v>3.543</v>
+        <v>3.5429</v>
       </c>
       <c r="V13" t="n">
         <v>-3.255</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9997</v>
+        <v>1.1069</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7023</v>
+        <v>0.8094</v>
       </c>
       <c r="F14" t="n">
         <v>0.2974</v>
@@ -1546,10 +1546,10 @@
         <v>0.4162</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8696</v>
+        <v>-0.7625</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1957</v>
+        <v>-0.0886</v>
       </c>
       <c r="U14" t="n">
         <v>-0.6739000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8017</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4586</v>
+        <v>0.5658</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3431</v>
+        <v>0.3137</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1662</v>
@@ -1624,13 +1624,13 @@
         <v>0.6244</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.824</v>
+        <v>-0.7462</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1305</v>
+        <v>-0.0233</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6935</v>
+        <v>-0.7228</v>
       </c>
       <c r="V15" t="n">
         <v>1.1675</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MENENDEZ GARCIA</t>
+          <t>S. BARROS GARCIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.292</v>
+        <v>0.0583</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3286</v>
+        <v>1.9908</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.6206</v>
+        <v>-1.9326</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.8904</v>
+        <v>-2.0777</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2217</v>
+        <v>2.1514</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.1121</v>
+        <v>-4.2291</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8167</v>
+        <v>1.1924</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5816</v>
+        <v>2.9314</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2351</v>
+        <v>-1.739</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.7071</v>
+        <v>-3.27</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.3599</v>
+        <v>-0.78</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.3472</v>
+        <v>-2.4901</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6244</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S16" t="n">
-        <v>0.974</v>
+        <v>-1.3885</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9687</v>
+        <v>-0.8529</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0053</v>
+        <v>-0.5356</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>3.7325</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5838</v>
+        <v>3.7325</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. BARROS GARCIA</t>
+          <t>J. MENENDEZ GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3219</v>
+        <v>-1.4913</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6694</v>
+        <v>2.3642</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9913</v>
+        <v>-3.8555</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.0777</v>
+        <v>-1.8904</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1514</v>
+        <v>0.2217</v>
       </c>
       <c r="I17" t="n">
-        <v>-4.2291</v>
+        <v>-2.1121</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1924</v>
+        <v>2.8167</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9314</v>
+        <v>2.5816</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.739</v>
+        <v>0.2351</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.27</v>
+        <v>-4.7071</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.78</v>
+        <v>-2.3599</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.4901</v>
+        <v>-2.3472</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7687</v>
+        <v>-0.2253</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1744</v>
+        <v>0.0043</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.2296</v>
       </c>
       <c r="V17" t="n">
-        <v>3.7325</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.7325</v>
+        <v>0.5838</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7043</v>
+        <v>-1.5472</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4635</v>
+        <v>-0.5706</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2409</v>
+        <v>-0.9766</v>
       </c>
       <c r="G18" t="n">
         <v>-1.2623</v>
@@ -1858,13 +1858,13 @@
         <v>0.8325</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4639</v>
+        <v>-0.3068</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.1757</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3953</v>
+        <v>-0.1311</v>
       </c>
       <c r="V18" t="n">
         <v>0.23</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1434</v>
+        <v>-1.8704</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6632</v>
+        <v>-0.4489</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4803</v>
+        <v>-1.4216</v>
       </c>
       <c r="G19" t="n">
         <v>-1.8939</v>
@@ -1936,13 +1936,13 @@
         <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.312</v>
+        <v>-1.0389</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3915</v>
+        <v>-0.1771</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9205</v>
+        <v>-0.8618</v>
       </c>
       <c r="V19" t="n">
         <v>0.23</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6596</v>
+        <v>-3.0222</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6958</v>
+        <v>2.8029</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.3553</v>
+        <v>-5.8251</v>
       </c>
       <c r="G20" t="n">
         <v>-3.1134</v>
@@ -2014,13 +2014,13 @@
         <v>2.4974</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.08939999999999999</v>
+        <v>-0.452</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5905</v>
+        <v>-0.4833</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5011</v>
+        <v>0.0314</v>
       </c>
       <c r="V20" t="n">
         <v>1.1675</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.1567</v>
+        <v>-4.4591</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.8233</v>
+        <v>-4.0376</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3334</v>
+        <v>-0.4215</v>
       </c>
       <c r="G21" t="n">
         <v>-3.2221</v>
@@ -2092,13 +2092,13 @@
         <v>1.0406</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.124</v>
+        <v>-0.4264</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0033</v>
+        <v>-0.2176</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1207</v>
+        <v>-0.2087</v>
       </c>
       <c r="V21" t="n">
         <v>0.23</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.0623</v>
+        <v>-5.0036</v>
       </c>
       <c r="E22" t="n">
         <v>-4.3005</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7618</v>
+        <v>-0.703</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3836</v>
@@ -2170,13 +2170,13 @@
         <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0543</v>
+        <v>-0.9956</v>
       </c>
       <c r="T22" t="n">
         <v>-0.8482</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2061</v>
+        <v>-0.1474</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5838</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.0232</v>
+        <v>-9.212899999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9945</v>
+        <v>-4.5658</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.0287</v>
+        <v>-4.647</v>
       </c>
       <c r="G23" t="n">
         <v>-4.2213</v>
@@ -2248,13 +2248,13 @@
         <v>1.6649</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4262</v>
+        <v>-0.6159</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1091</v>
+        <v>-0.6805</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3171</v>
+        <v>0.0646</v>
       </c>
       <c r="V23" t="n">
         <v>-2.9188</v>
@@ -2284,7 +2284,7 @@
         <v>-24.562</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.390300000000002</v>
+        <v>-5.390300000000001</v>
       </c>
       <c r="F24" t="n">
         <v>-19.1718</v>
@@ -2329,10 +2329,10 @@
         <v>-6.9581</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.543</v>
+        <v>-3.5429</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.415</v>
+        <v>-3.4149</v>
       </c>
       <c r="V24" t="n">
         <v>3.2549</v>
